--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>951575.5</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>885234</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>877160</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>804500</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>804293</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>793415</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>766195</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>748930</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>745490</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>742330</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>739580</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>733400</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>726660</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>723615</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>704038</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>700000</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>687510</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>687500</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>687500</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>679116</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>670800</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>670583</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>662495</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>661755</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>658120</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>653919</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>648125</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>647540</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>636398</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>631250</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>625000</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>616319</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>616110.5</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>614660</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>611097.5</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>600000</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>600000</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -876,9 +760,6 @@
       </c>
       <c r="B39">
         <v>580504</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>951575.5</v>
       </c>
+      <c r="C2">
+        <v>817531</v>
+      </c>
+      <c r="D2">
+        <v>134044.5</v>
+      </c>
+      <c r="E2">
+        <v>16.39625897978181</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>885234</v>
       </c>
+      <c r="C3">
+        <v>767740</v>
+      </c>
+      <c r="D3">
+        <v>117494</v>
+      </c>
+      <c r="E3">
+        <v>15.30387891734182</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>877160</v>
       </c>
+      <c r="C4">
+        <v>695210</v>
+      </c>
+      <c r="D4">
+        <v>181950</v>
+      </c>
+      <c r="E4">
+        <v>26.17194804447578</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,16 +448,34 @@
       <c r="B5">
         <v>804500</v>
       </c>
+      <c r="C5">
+        <v>697340</v>
+      </c>
+      <c r="D5">
+        <v>107160</v>
+      </c>
+      <c r="E5">
+        <v>15.36696589898758</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Juan Fernandez</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="B6">
         <v>804293</v>
       </c>
+      <c r="C6">
+        <v>713160</v>
+      </c>
+      <c r="D6">
+        <v>91133</v>
+      </c>
+      <c r="E6">
+        <v>12.77875932469572</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>793415</v>
       </c>
+      <c r="C7">
+        <v>687750</v>
+      </c>
+      <c r="D7">
+        <v>105665</v>
+      </c>
+      <c r="E7">
+        <v>15.36386768447837</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>766195</v>
       </c>
+      <c r="C8">
+        <v>667712</v>
+      </c>
+      <c r="D8">
+        <v>98483</v>
+      </c>
+      <c r="E8">
+        <v>14.74932306143966</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>748930</v>
       </c>
+      <c r="C9">
+        <v>633500.5</v>
+      </c>
+      <c r="D9">
+        <v>115429.5</v>
+      </c>
+      <c r="E9">
+        <v>18.2209011674024</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -481,6 +553,15 @@
       <c r="B11">
         <v>742330</v>
       </c>
+      <c r="C11">
+        <v>660000</v>
+      </c>
+      <c r="D11">
+        <v>82330</v>
+      </c>
+      <c r="E11">
+        <v>12.47424242424242</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +572,15 @@
       <c r="B12">
         <v>739580</v>
       </c>
+      <c r="C12">
+        <v>642625</v>
+      </c>
+      <c r="D12">
+        <v>96955</v>
+      </c>
+      <c r="E12">
+        <v>15.0873370939506</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +591,15 @@
       <c r="B13">
         <v>733400</v>
       </c>
+      <c r="C13">
+        <v>613814</v>
+      </c>
+      <c r="D13">
+        <v>119586</v>
+      </c>
+      <c r="E13">
+        <v>19.48244908066612</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +610,15 @@
       <c r="B14">
         <v>726660</v>
       </c>
+      <c r="C14">
+        <v>637047</v>
+      </c>
+      <c r="D14">
+        <v>89613</v>
+      </c>
+      <c r="E14">
+        <v>14.06693697639263</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,6 +629,15 @@
       <c r="B15">
         <v>723615</v>
       </c>
+      <c r="C15">
+        <v>642950</v>
+      </c>
+      <c r="D15">
+        <v>80665</v>
+      </c>
+      <c r="E15">
+        <v>12.5460766778132</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -531,6 +648,15 @@
       <c r="B16">
         <v>704038</v>
       </c>
+      <c r="C16">
+        <v>622573.5</v>
+      </c>
+      <c r="D16">
+        <v>81464.5</v>
+      </c>
+      <c r="E16">
+        <v>13.08512167639644</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -541,225 +667,442 @@
       <c r="B17">
         <v>700000</v>
       </c>
+      <c r="C17">
+        <v>623240</v>
+      </c>
+      <c r="D17">
+        <v>76760</v>
+      </c>
+      <c r="E17">
+        <v>12.31628265194789</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B18">
-        <v>687510</v>
+        <v>700000</v>
+      </c>
+      <c r="C18">
+        <v>612521</v>
+      </c>
+      <c r="D18">
+        <v>87479</v>
+      </c>
+      <c r="E18">
+        <v>14.28179605270676</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B19">
-        <v>687500</v>
+        <v>687510</v>
+      </c>
+      <c r="C19">
+        <v>597318.5</v>
+      </c>
+      <c r="D19">
+        <v>90191.5</v>
+      </c>
+      <c r="E19">
+        <v>15.09939839465879</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="B20">
         <v>687500</v>
       </c>
+      <c r="C20">
+        <v>588675</v>
+      </c>
+      <c r="D20">
+        <v>98825</v>
+      </c>
+      <c r="E20">
+        <v>16.78770119335798</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="B21">
-        <v>679116</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="B22">
-        <v>670800</v>
+        <v>679116</v>
+      </c>
+      <c r="C22">
+        <v>551809</v>
+      </c>
+      <c r="D22">
+        <v>127307</v>
+      </c>
+      <c r="E22">
+        <v>23.07084516562796</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B23">
-        <v>670583</v>
+        <v>670800</v>
+      </c>
+      <c r="C23">
+        <v>595890</v>
+      </c>
+      <c r="D23">
+        <v>74910</v>
+      </c>
+      <c r="E23">
+        <v>12.57111211800837</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B24">
-        <v>662495</v>
+        <v>670583</v>
+      </c>
+      <c r="C24">
+        <v>586620</v>
+      </c>
+      <c r="D24">
+        <v>83963</v>
+      </c>
+      <c r="E24">
+        <v>14.31301353516756</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B25">
-        <v>661755</v>
+        <v>662495</v>
+      </c>
+      <c r="C25">
+        <v>580570</v>
+      </c>
+      <c r="D25">
+        <v>81925</v>
+      </c>
+      <c r="E25">
+        <v>14.11113216321891</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B26">
-        <v>658120</v>
+        <v>661755</v>
+      </c>
+      <c r="C26">
+        <v>588290</v>
+      </c>
+      <c r="D26">
+        <v>73465</v>
+      </c>
+      <c r="E26">
+        <v>12.48788862635775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="B27">
-        <v>653919</v>
+        <v>658120</v>
+      </c>
+      <c r="C27">
+        <v>589679</v>
+      </c>
+      <c r="D27">
+        <v>68441</v>
+      </c>
+      <c r="E27">
+        <v>11.60648420581367</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="B28">
-        <v>648125</v>
+        <v>653919</v>
+      </c>
+      <c r="C28">
+        <v>575906</v>
+      </c>
+      <c r="D28">
+        <v>78013</v>
+      </c>
+      <c r="E28">
+        <v>13.54613426496685</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="B29">
-        <v>647540</v>
+        <v>648125</v>
+      </c>
+      <c r="C29">
+        <v>560837</v>
+      </c>
+      <c r="D29">
+        <v>87288</v>
+      </c>
+      <c r="E29">
+        <v>15.56388041445198</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="B30">
-        <v>636398</v>
+        <v>647540</v>
+      </c>
+      <c r="C30">
+        <v>559980</v>
+      </c>
+      <c r="D30">
+        <v>87560</v>
+      </c>
+      <c r="E30">
+        <v>15.63627272402586</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="B31">
-        <v>631250</v>
+        <v>636398</v>
+      </c>
+      <c r="C31">
+        <v>568991</v>
+      </c>
+      <c r="D31">
+        <v>67407</v>
+      </c>
+      <c r="E31">
+        <v>11.84676031782577</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="B32">
-        <v>625000</v>
+        <v>631250</v>
+      </c>
+      <c r="C32">
+        <v>542282.5</v>
+      </c>
+      <c r="D32">
+        <v>88967.5</v>
+      </c>
+      <c r="E32">
+        <v>16.40611673804706</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="B33">
-        <v>616319</v>
+        <v>625000</v>
+      </c>
+      <c r="C33">
+        <v>541920</v>
+      </c>
+      <c r="D33">
+        <v>83080</v>
+      </c>
+      <c r="E33">
+        <v>15.33067611455565</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B34">
-        <v>616110.5</v>
+        <v>616319</v>
+      </c>
+      <c r="C34">
+        <v>534240</v>
+      </c>
+      <c r="D34">
+        <v>82079</v>
+      </c>
+      <c r="E34">
+        <v>15.36369421982629</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="B35">
-        <v>614660</v>
+        <v>616110.5</v>
+      </c>
+      <c r="C35">
+        <v>542023</v>
+      </c>
+      <c r="D35">
+        <v>74087.5</v>
+      </c>
+      <c r="E35">
+        <v>13.66870040570234</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="B36">
-        <v>611097.5</v>
+        <v>614660</v>
+      </c>
+      <c r="C36">
+        <v>529218.5</v>
+      </c>
+      <c r="D36">
+        <v>85441.5</v>
+      </c>
+      <c r="E36">
+        <v>16.14484376490996</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="B37">
-        <v>600000</v>
+        <v>611097.5</v>
+      </c>
+      <c r="C37">
+        <v>539206</v>
+      </c>
+      <c r="D37">
+        <v>71891.5</v>
+      </c>
+      <c r="E37">
+        <v>13.33284496092402</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="B38">
         <v>600000</v>
       </c>
+      <c r="C38">
+        <v>521186</v>
+      </c>
+      <c r="D38">
+        <v>78814</v>
+      </c>
+      <c r="E38">
+        <v>15.12204855848007</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>La Ligua</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>600000</v>
+      </c>
+      <c r="C39">
+        <v>523170</v>
+      </c>
+      <c r="D39">
+        <v>76830</v>
+      </c>
+      <c r="E39">
+        <v>14.68547508458053</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Olmué</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>580504</v>
+      </c>
+      <c r="C40">
+        <v>496218</v>
+      </c>
+      <c r="D40">
+        <v>84286</v>
+      </c>
+      <c r="E40">
+        <v>16.98567968110789</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -1112,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1121,20 +1121,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>687500</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1143,48 +1135,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>653919</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>687500</v>
+          <t>Petorca</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>739580</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>611097.5</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>687510</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1193,148 +1170,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>704038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>951575.5</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>600000</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>658120</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>648125</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>885234</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>600000</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>614660</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>745490</v>
+          <t>El Quisco</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>804500</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>766195</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>580504</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>636398</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>631250</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>616319</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1343,148 +1275,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>647540</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>616110.5</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>670583</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>742330</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>700000</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>733400</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>661755</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>748930</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>662495</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>625000</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>793415</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>670800</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>723615</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>726660</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>679116</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
